--- a/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9744595F-4C5F-4D11-AF4B-CE7A8181E5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C365EA8-7FDC-4C9A-ACCF-52B1E25379F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="210">
   <si>
     <t>ソフトウェア仕様書 WBS（Work Breakdown Structure）</t>
   </si>
@@ -658,6 +658,13 @@
   </si>
   <si>
     <t>かえ</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
     <phoneticPr fontId="7"/>
   </si>
 </sst>
@@ -1193,15 +1200,16 @@
   <dimension ref="A1:K141"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1321,7 +1329,7 @@
         <v>16</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K6" s="8"/>
     </row>

--- a/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C365EA8-7FDC-4C9A-ACCF-52B1E25379F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C34BFD-2D4B-4ED0-9F8B-A75D204BEED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WBS!$A$2:$K$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WBS!$A$2:$K$142</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="215">
   <si>
     <t>ソフトウェア仕様書 WBS（Work Breakdown Structure）</t>
   </si>
@@ -664,6 +664,50 @@
     <t>完了</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>外部サービス連携方針記載</t>
+    <rPh sb="0" eb="2">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウシン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>データ保護・プライバシー方針</t>
+    <rPh sb="3" eb="5">
+      <t>ホゴ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ホウシン</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>かえ</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>赤木</t>
+    <rPh sb="0" eb="2">
+      <t>アカギ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -1197,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
@@ -1306,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="K5" s="5"/>
     </row>
@@ -1352,7 +1396,7 @@
         <v>16</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K7" s="8"/>
     </row>
@@ -1375,7 +1419,7 @@
         <v>16</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K8" s="8"/>
     </row>
@@ -1402,7 +1446,7 @@
         <v>16</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="K9" s="5"/>
     </row>
@@ -1425,7 +1469,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K10" s="8"/>
     </row>
@@ -1448,7 +1492,7 @@
         <v>16</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K11" s="8"/>
     </row>
@@ -1471,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K12" s="8"/>
     </row>
@@ -1498,7 +1542,7 @@
         <v>28</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>17</v>
+        <v>210</v>
       </c>
       <c r="K13" s="5"/>
     </row>
@@ -1521,7 +1565,7 @@
         <v>28</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K14" s="8"/>
     </row>
@@ -1544,7 +1588,7 @@
         <v>28</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K15" s="8"/>
     </row>
@@ -1729,7 +1773,9 @@
       <c r="G23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="8" t="s">
+        <v>208</v>
+      </c>
       <c r="I23" s="9" t="s">
         <v>16</v>
       </c>
@@ -1752,7 +1798,9 @@
       <c r="G24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H24" s="8"/>
+      <c r="H24" s="8" t="s">
+        <v>214</v>
+      </c>
       <c r="I24" s="9" t="s">
         <v>16</v>
       </c>
@@ -1775,7 +1823,9 @@
       <c r="G25" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H25" s="8"/>
+      <c r="H25" s="8" t="s">
+        <v>213</v>
+      </c>
       <c r="I25" s="9" t="s">
         <v>16</v>
       </c>
@@ -1798,7 +1848,9 @@
       <c r="G26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="H26" s="8"/>
+      <c r="H26" s="8" t="s">
+        <v>213</v>
+      </c>
       <c r="I26" s="11" t="s">
         <v>28</v>
       </c>
@@ -1807,7 +1859,7 @@
       </c>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7">
         <v>24</v>
       </c>
@@ -1821,7 +1873,9 @@
       <c r="G27" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H27" s="8"/>
+      <c r="H27" s="8" t="s">
+        <v>214</v>
+      </c>
       <c r="I27" s="11" t="s">
         <v>28</v>
       </c>
@@ -1830,182 +1884,186 @@
       </c>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="2">
+    <row r="28" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="7">
         <v>25</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="7">
+        <v>26</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>25</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="4">
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="4">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5" t="s">
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="5"/>
-    </row>
-    <row r="30" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="12">
+      <c r="I31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="12">
         <v>27</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B32" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13" t="s">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E32" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="13"/>
-    </row>
-    <row r="31" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="15">
-        <v>28</v>
-      </c>
-      <c r="B31" s="16" t="s">
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="13"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="15">
+        <v>28</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16" t="s">
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" s="16"/>
-    </row>
-    <row r="32" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="7">
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="7">
         <v>29</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8" t="s">
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H32" s="8"/>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="8"/>
-    </row>
-    <row r="33" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="7">
-        <v>30</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="8"/>
-    </row>
-    <row r="34" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="15">
-        <v>31</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" s="16"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="8"/>
     </row>
     <row r="35" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="9" t="s">
@@ -2017,31 +2075,31 @@
       <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="7">
-        <v>33</v>
-      </c>
-      <c r="B36" s="8" t="s">
+      <c r="A36" s="15">
+        <v>31</v>
+      </c>
+      <c r="B36" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="8"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="16"/>
     </row>
     <row r="37" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>56</v>
@@ -2051,7 +2109,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="9" t="s">
@@ -2063,41 +2121,41 @@
       <c r="K37" s="8"/>
     </row>
     <row r="38" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="15">
-        <v>35</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="16"/>
+      <c r="A38" s="7">
+        <v>33</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" s="8"/>
+      <c r="I38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H39" s="8"/>
       <c r="I39" s="9" t="s">
@@ -2109,31 +2167,31 @@
       <c r="K39" s="8"/>
     </row>
     <row r="40" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="7">
-        <v>37</v>
-      </c>
-      <c r="B40" s="8" t="s">
+      <c r="A40" s="15">
+        <v>35</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H40" s="8"/>
-      <c r="I40" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" s="8"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="16"/>
     </row>
     <row r="41" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>61</v>
@@ -2143,7 +2201,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H41" s="8"/>
       <c r="I41" s="9" t="s">
@@ -2155,135 +2213,135 @@
       <c r="K41" s="8"/>
     </row>
     <row r="42" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="12">
+      <c r="A42" s="7">
+        <v>37</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H42" s="8"/>
+      <c r="I42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="8"/>
+    </row>
+    <row r="43" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="7">
+        <v>38</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H43" s="8"/>
+      <c r="I43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="8"/>
+    </row>
+    <row r="44" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="12">
         <v>39</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B44" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13" t="s">
+      <c r="C44" s="13"/>
+      <c r="D44" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E44" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" s="13"/>
-    </row>
-    <row r="43" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="15">
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="13"/>
+    </row>
+    <row r="45" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="15">
         <v>40</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B45" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16" t="s">
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="16"/>
-    </row>
-    <row r="44" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="7">
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="16"/>
+    </row>
+    <row r="46" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="7">
         <v>41</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B46" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8" t="s">
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H44" s="8"/>
-      <c r="I44" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="8"/>
-    </row>
-    <row r="45" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="7">
-        <v>42</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H45" s="8"/>
-      <c r="I45" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" s="8"/>
-    </row>
-    <row r="46" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="15">
-        <v>43</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="16"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="8"/>
     </row>
     <row r="47" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H47" s="8"/>
       <c r="I47" s="9" t="s">
@@ -2295,31 +2353,31 @@
       <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="7">
-        <v>45</v>
-      </c>
-      <c r="B48" s="8" t="s">
+      <c r="A48" s="15">
+        <v>43</v>
+      </c>
+      <c r="B48" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H48" s="8"/>
-      <c r="I48" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K48" s="8"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="16"/>
     </row>
     <row r="49" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>71</v>
@@ -2329,7 +2387,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H49" s="8"/>
       <c r="I49" s="9" t="s">
@@ -2341,41 +2399,41 @@
       <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="15">
-        <v>47</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K50" s="16"/>
+      <c r="A50" s="7">
+        <v>45</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="8"/>
+      <c r="I50" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="8"/>
     </row>
     <row r="51" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="9" t="s">
@@ -2387,31 +2445,31 @@
       <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="7">
-        <v>49</v>
-      </c>
-      <c r="B52" s="8" t="s">
+      <c r="A52" s="15">
+        <v>47</v>
+      </c>
+      <c r="B52" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H52" s="8"/>
-      <c r="I52" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" s="8"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="16"/>
     </row>
     <row r="53" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>76</v>
@@ -2421,7 +2479,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H53" s="8"/>
       <c r="I53" s="9" t="s">
@@ -2433,87 +2491,87 @@
       <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="12">
+      <c r="A54" s="7">
+        <v>49</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H54" s="8"/>
+      <c r="I54" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="8"/>
+    </row>
+    <row r="55" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="7">
+        <v>50</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H55" s="8"/>
+      <c r="I55" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" s="8"/>
+    </row>
+    <row r="56" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="12">
         <v>51</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B56" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13" t="s">
+      <c r="C56" s="13"/>
+      <c r="D56" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E56" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K54" s="13"/>
-    </row>
-    <row r="55" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="15">
-        <v>52</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K55" s="16"/>
-    </row>
-    <row r="56" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="7">
-        <v>53</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H56" s="8"/>
-      <c r="I56" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K56" s="8"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="15">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
       <c r="E57" s="16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F57" s="16"/>
       <c r="G57" s="16"/>
@@ -2528,17 +2586,17 @@
     </row>
     <row r="58" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="7">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="9" t="s">
@@ -2550,64 +2608,64 @@
       <c r="K58" s="8"/>
     </row>
     <row r="59" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="7">
-        <v>56</v>
-      </c>
-      <c r="B59" s="8" t="s">
+      <c r="A59" s="15">
+        <v>54</v>
+      </c>
+      <c r="B59" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H59" s="8"/>
-      <c r="I59" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K59" s="8"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="16"/>
     </row>
     <row r="60" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="15">
-        <v>57</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-      <c r="I60" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K60" s="16"/>
+      <c r="A60" s="7">
+        <v>55</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H60" s="8"/>
+      <c r="I60" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" s="8"/>
     </row>
     <row r="61" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="7">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="9" t="s">
@@ -2618,138 +2676,138 @@
       </c>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="7">
+    <row r="62" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="15">
+        <v>57</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" s="16"/>
+      <c r="G62" s="16"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="16"/>
+    </row>
+    <row r="63" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="7">
+        <v>58</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H63" s="8"/>
+      <c r="I63" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="8"/>
+    </row>
+    <row r="64" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="7">
         <v>59</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B64" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8" t="s">
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="H62" s="8"/>
-      <c r="I62" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K62" s="8"/>
-    </row>
-    <row r="63" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="4">
+      <c r="H64" s="8"/>
+      <c r="I64" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" s="8"/>
+    </row>
+    <row r="65" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="4">
         <v>60</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B65" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5" t="s">
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I63" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K63" s="5"/>
-    </row>
-    <row r="64" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="12">
+      <c r="I65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" s="5"/>
+    </row>
+    <row r="66" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="12">
         <v>61</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B66" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13" t="s">
+      <c r="C66" s="13"/>
+      <c r="D66" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E66" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K64" s="13"/>
-    </row>
-    <row r="65" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="15">
-        <v>62</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K65" s="16"/>
-    </row>
-    <row r="66" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="7">
-        <v>63</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H66" s="8"/>
-      <c r="I66" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K66" s="8"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="13"/>
     </row>
     <row r="67" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="15">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C67" s="16"/>
       <c r="D67" s="16"/>
       <c r="E67" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F67" s="16"/>
       <c r="G67" s="16"/>
@@ -2764,17 +2822,17 @@
     </row>
     <row r="68" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="7">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="9" t="s">
@@ -2786,31 +2844,31 @@
       <c r="K68" s="8"/>
     </row>
     <row r="69" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="7">
-        <v>66</v>
-      </c>
-      <c r="B69" s="8" t="s">
+      <c r="A69" s="15">
+        <v>64</v>
+      </c>
+      <c r="B69" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H69" s="8"/>
-      <c r="I69" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K69" s="8"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69" s="16"/>
     </row>
     <row r="70" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="7">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>99</v>
@@ -2820,7 +2878,7 @@
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="9" t="s">
@@ -2832,41 +2890,41 @@
       <c r="K70" s="8"/>
     </row>
     <row r="71" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="15">
-        <v>68</v>
-      </c>
-      <c r="B71" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="16"/>
-      <c r="I71" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K71" s="16"/>
+      <c r="A71" s="7">
+        <v>66</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H71" s="8"/>
+      <c r="I71" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K71" s="8"/>
     </row>
     <row r="72" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="7">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="9" t="s">
@@ -2878,110 +2936,110 @@
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="7">
+      <c r="A73" s="15">
+        <v>68</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="16"/>
+    </row>
+    <row r="74" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="7">
+        <v>69</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H74" s="8"/>
+      <c r="I74" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" s="8"/>
+    </row>
+    <row r="75" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="7">
         <v>70</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B75" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8" t="s">
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H73" s="8"/>
-      <c r="I73" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K73" s="8"/>
-    </row>
-    <row r="74" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="12">
+      <c r="H75" s="8"/>
+      <c r="I75" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" s="8"/>
+    </row>
+    <row r="76" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="12">
         <v>71</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B76" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13" t="s">
+      <c r="C76" s="13"/>
+      <c r="D76" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E76" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K74" s="13"/>
-    </row>
-    <row r="75" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="15">
-        <v>72</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
-      <c r="I75" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J75" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K75" s="16"/>
-    </row>
-    <row r="76" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="7">
-        <v>73</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H76" s="8"/>
-      <c r="I76" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J76" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K76" s="8"/>
+      <c r="F76" s="13"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="13"/>
     </row>
     <row r="77" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="15">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C77" s="16"/>
       <c r="D77" s="16"/>
       <c r="E77" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F77" s="16"/>
       <c r="G77" s="16"/>
@@ -2996,17 +3054,17 @@
     </row>
     <row r="78" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="7">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="H78" s="8"/>
       <c r="I78" s="9" t="s">
@@ -3018,31 +3076,31 @@
       <c r="K78" s="8"/>
     </row>
     <row r="79" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="7">
-        <v>76</v>
-      </c>
-      <c r="B79" s="8" t="s">
+      <c r="A79" s="15">
+        <v>74</v>
+      </c>
+      <c r="B79" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="H79" s="8"/>
-      <c r="I79" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K79" s="8"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" s="16"/>
     </row>
     <row r="80" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="7">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>112</v>
@@ -3052,7 +3110,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H80" s="8"/>
       <c r="I80" s="9" t="s">
@@ -3064,41 +3122,41 @@
       <c r="K80" s="8"/>
     </row>
     <row r="81" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="15">
-        <v>78</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
-      <c r="H81" s="16"/>
-      <c r="I81" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J81" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K81" s="16"/>
+      <c r="A81" s="7">
+        <v>76</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H81" s="8"/>
+      <c r="I81" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="8"/>
     </row>
     <row r="82" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="7">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
       <c r="G82" s="8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H82" s="8"/>
       <c r="I82" s="9" t="s">
@@ -3110,31 +3168,31 @@
       <c r="K82" s="8"/>
     </row>
     <row r="83" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="7">
-        <v>80</v>
-      </c>
-      <c r="B83" s="8" t="s">
+      <c r="A83" s="15">
+        <v>78</v>
+      </c>
+      <c r="B83" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="H83" s="8"/>
-      <c r="I83" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K83" s="8"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="16"/>
     </row>
     <row r="84" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="7">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>117</v>
@@ -3144,99 +3202,99 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H84" s="8"/>
+      <c r="I84" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" s="8"/>
+    </row>
+    <row r="85" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="7">
+        <v>80</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="H85" s="8"/>
+      <c r="I85" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85" s="8"/>
+    </row>
+    <row r="86" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="7">
+        <v>81</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H84" s="8"/>
-      <c r="I84" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K84" s="8"/>
-    </row>
-    <row r="85" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="12">
+      <c r="H86" s="8"/>
+      <c r="I86" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" s="8"/>
+    </row>
+    <row r="87" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A87" s="12">
         <v>82</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B87" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13" t="s">
+      <c r="C87" s="13"/>
+      <c r="D87" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E85" s="13" t="s">
+      <c r="E87" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J85" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K85" s="13"/>
-    </row>
-    <row r="86" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="15">
-        <v>83</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-      <c r="H86" s="16"/>
-      <c r="I86" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J86" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K86" s="16"/>
-    </row>
-    <row r="87" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="7">
-        <v>84</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H87" s="8"/>
-      <c r="I87" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K87" s="8"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="13"/>
     </row>
     <row r="88" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C88" s="16"/>
       <c r="D88" s="16"/>
       <c r="E88" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
@@ -3251,17 +3309,17 @@
     </row>
     <row r="89" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="7">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="8" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="H89" s="8"/>
       <c r="I89" s="11" t="s">
@@ -3274,15 +3332,15 @@
     </row>
     <row r="90" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="15">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
@@ -3297,17 +3355,17 @@
     </row>
     <row r="91" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="7">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
       <c r="G91" s="8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="11" t="s">
@@ -3318,138 +3376,138 @@
       </c>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="7">
+    <row r="92" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A92" s="15">
+        <v>87</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K92" s="16"/>
+    </row>
+    <row r="93" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="7">
+        <v>88</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H93" s="8"/>
+      <c r="I93" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K93" s="8"/>
+    </row>
+    <row r="94" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="7">
         <v>89</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B94" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8" t="s">
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="H92" s="8"/>
-      <c r="I92" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K92" s="8"/>
-    </row>
-    <row r="93" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="4">
+      <c r="H94" s="8"/>
+      <c r="I94" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94" s="8"/>
+    </row>
+    <row r="95" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A95" s="4">
         <v>90</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B95" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C95" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D93" s="5" t="s">
+      <c r="D95" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5" t="s">
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="I93" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J93" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K93" s="5"/>
-    </row>
-    <row r="94" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="12">
+      <c r="I95" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K95" s="5"/>
+    </row>
+    <row r="96" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="12">
         <v>91</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B96" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C94" s="13"/>
-      <c r="D94" s="13" t="s">
+      <c r="C96" s="13"/>
+      <c r="D96" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E94" s="13" t="s">
+      <c r="E96" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J94" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K94" s="13"/>
-    </row>
-    <row r="95" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="15">
-        <v>92</v>
-      </c>
-      <c r="B95" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C95" s="16"/>
-      <c r="D95" s="16"/>
-      <c r="E95" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
-      <c r="H95" s="16"/>
-      <c r="I95" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J95" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K95" s="16"/>
-    </row>
-    <row r="96" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="7">
-        <v>93</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H96" s="8"/>
-      <c r="I96" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K96" s="8"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K96" s="13"/>
     </row>
     <row r="97" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="15">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C97" s="16"/>
       <c r="D97" s="16"/>
       <c r="E97" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
@@ -3464,17 +3522,17 @@
     </row>
     <row r="98" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
       <c r="G98" s="8" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="11" t="s">
@@ -3486,64 +3544,64 @@
       <c r="K98" s="8"/>
     </row>
     <row r="99" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="7">
-        <v>96</v>
-      </c>
-      <c r="B99" s="8" t="s">
+      <c r="A99" s="15">
+        <v>94</v>
+      </c>
+      <c r="B99" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="H99" s="8"/>
-      <c r="I99" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J99" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K99" s="8"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F99" s="16"/>
+      <c r="G99" s="16"/>
+      <c r="H99" s="16"/>
+      <c r="I99" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K99" s="16"/>
     </row>
     <row r="100" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="15">
-        <v>97</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C100" s="16"/>
-      <c r="D100" s="16"/>
-      <c r="E100" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="F100" s="16"/>
-      <c r="G100" s="16"/>
-      <c r="H100" s="16"/>
-      <c r="I100" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J100" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K100" s="16"/>
+      <c r="A100" s="7">
+        <v>95</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H100" s="8"/>
+      <c r="I100" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K100" s="8"/>
     </row>
     <row r="101" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="7">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H101" s="8"/>
       <c r="I101" s="11" t="s">
@@ -3555,112 +3613,112 @@
       <c r="K101" s="8"/>
     </row>
     <row r="102" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="7">
+      <c r="A102" s="15">
+        <v>97</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F102" s="16"/>
+      <c r="G102" s="16"/>
+      <c r="H102" s="16"/>
+      <c r="I102" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J102" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K102" s="16"/>
+    </row>
+    <row r="103" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A103" s="7">
+        <v>98</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H103" s="8"/>
+      <c r="I103" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K103" s="8"/>
+    </row>
+    <row r="104" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A104" s="7">
         <v>99</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B104" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8" t="s">
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="H102" s="8"/>
-      <c r="I102" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K102" s="8" t="s">
+      <c r="H104" s="8"/>
+      <c r="I104" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K104" s="8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="12">
+    <row r="105" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A105" s="12">
         <v>100</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B105" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C103" s="13"/>
-      <c r="D103" s="13" t="s">
+      <c r="C105" s="13"/>
+      <c r="D105" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E103" s="13" t="s">
+      <c r="E105" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J103" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K103" s="13"/>
-    </row>
-    <row r="104" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="15">
-        <v>101</v>
-      </c>
-      <c r="B104" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="C104" s="16"/>
-      <c r="D104" s="16"/>
-      <c r="E104" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="F104" s="16"/>
-      <c r="G104" s="16"/>
-      <c r="H104" s="16"/>
-      <c r="I104" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J104" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K104" s="16"/>
-    </row>
-    <row r="105" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="7">
-        <v>102</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H105" s="8"/>
-      <c r="I105" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J105" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K105" s="8"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K105" s="13"/>
     </row>
     <row r="106" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="15">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C106" s="16"/>
       <c r="D106" s="16"/>
       <c r="E106" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F106" s="16"/>
       <c r="G106" s="16"/>
@@ -3675,17 +3733,17 @@
     </row>
     <row r="107" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="7">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
       <c r="G107" s="8" t="s">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="11" t="s">
@@ -3697,64 +3755,64 @@
       <c r="K107" s="8"/>
     </row>
     <row r="108" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A108" s="7">
-        <v>105</v>
-      </c>
-      <c r="B108" s="8" t="s">
+      <c r="A108" s="15">
+        <v>103</v>
+      </c>
+      <c r="B108" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H108" s="8"/>
-      <c r="I108" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J108" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K108" s="8"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="F108" s="16"/>
+      <c r="G108" s="16"/>
+      <c r="H108" s="16"/>
+      <c r="I108" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K108" s="16"/>
     </row>
     <row r="109" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="15">
-        <v>106</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C109" s="16"/>
-      <c r="D109" s="16"/>
-      <c r="E109" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="F109" s="16"/>
-      <c r="G109" s="16"/>
-      <c r="H109" s="16"/>
-      <c r="I109" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J109" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K109" s="16"/>
+      <c r="A109" s="7">
+        <v>104</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H109" s="8"/>
+      <c r="I109" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K109" s="8"/>
     </row>
     <row r="110" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="7">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
       <c r="G110" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H110" s="8"/>
       <c r="I110" s="11" t="s">
@@ -3765,138 +3823,138 @@
       </c>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A111" s="7">
+    <row r="111" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="15">
+        <v>106</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C111" s="16"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J111" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K111" s="16"/>
+    </row>
+    <row r="112" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A112" s="7">
+        <v>107</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H112" s="8"/>
+      <c r="I112" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K112" s="8"/>
+    </row>
+    <row r="113" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A113" s="7">
         <v>108</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="B113" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8" t="s">
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="H111" s="8"/>
-      <c r="I111" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J111" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K111" s="8"/>
-    </row>
-    <row r="112" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A112" s="4">
+      <c r="H113" s="8"/>
+      <c r="I113" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K113" s="8"/>
+    </row>
+    <row r="114" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="4">
         <v>109</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B114" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C114" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D114" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="5" t="s">
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="I112" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J112" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K112" s="5"/>
-    </row>
-    <row r="113" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A113" s="12">
+      <c r="I114" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K114" s="5"/>
+    </row>
+    <row r="115" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="12">
         <v>110</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B115" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C113" s="13"/>
-      <c r="D113" s="13" t="s">
+      <c r="C115" s="13"/>
+      <c r="D115" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="E115" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J113" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K113" s="13"/>
-    </row>
-    <row r="114" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="15">
-        <v>111</v>
-      </c>
-      <c r="B114" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="C114" s="16"/>
-      <c r="D114" s="16"/>
-      <c r="E114" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="F114" s="16"/>
-      <c r="G114" s="16"/>
-      <c r="H114" s="16"/>
-      <c r="I114" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J114" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K114" s="16"/>
-    </row>
-    <row r="115" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A115" s="7">
-        <v>112</v>
-      </c>
-      <c r="B115" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H115" s="8"/>
-      <c r="I115" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K115" s="8"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
+      <c r="I115" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J115" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K115" s="13"/>
     </row>
     <row r="116" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="15">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C116" s="16"/>
       <c r="D116" s="16"/>
       <c r="E116" s="16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F116" s="16"/>
       <c r="G116" s="16"/>
@@ -3911,17 +3969,17 @@
     </row>
     <row r="117" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="7">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="H117" s="8"/>
       <c r="I117" s="11" t="s">
@@ -3934,15 +3992,15 @@
     </row>
     <row r="118" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="15">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C118" s="16"/>
       <c r="D118" s="16"/>
       <c r="E118" s="16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F118" s="16"/>
       <c r="G118" s="16"/>
@@ -3957,17 +4015,17 @@
     </row>
     <row r="119" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="7">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
       <c r="G119" s="8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H119" s="8"/>
       <c r="I119" s="11" t="s">
@@ -3978,140 +4036,140 @@
       </c>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A120" s="7">
+    <row r="120" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="15">
+        <v>115</v>
+      </c>
+      <c r="B120" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C120" s="16"/>
+      <c r="D120" s="16"/>
+      <c r="E120" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="F120" s="16"/>
+      <c r="G120" s="16"/>
+      <c r="H120" s="16"/>
+      <c r="I120" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J120" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K120" s="16"/>
+    </row>
+    <row r="121" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A121" s="7">
+        <v>116</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="8"/>
+      <c r="G121" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H121" s="8"/>
+      <c r="I121" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J121" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K121" s="8"/>
+    </row>
+    <row r="122" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A122" s="7">
         <v>117</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B122" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="8"/>
-      <c r="G120" s="8" t="s">
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="H120" s="8"/>
-      <c r="I120" s="20" t="s">
+      <c r="H122" s="8"/>
+      <c r="I122" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="J120" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K120" s="8" t="s">
+      <c r="J122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K122" s="8" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A121" s="4">
+    <row r="123" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A123" s="4">
         <v>118</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B123" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C121" s="5" t="s">
+      <c r="C123" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D121" s="5" t="s">
+      <c r="D123" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="5" t="s">
+      <c r="E123" s="5"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I121" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K121" s="5"/>
-    </row>
-    <row r="122" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A122" s="12">
+      <c r="I123" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K123" s="5"/>
+    </row>
+    <row r="124" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A124" s="12">
         <v>119</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B124" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13" t="s">
+      <c r="C124" s="13"/>
+      <c r="D124" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="E122" s="13" t="s">
+      <c r="E124" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J122" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K122" s="13"/>
-    </row>
-    <row r="123" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="15">
-        <v>120</v>
-      </c>
-      <c r="B123" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="C123" s="16"/>
-      <c r="D123" s="16"/>
-      <c r="E123" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="F123" s="16"/>
-      <c r="G123" s="16"/>
-      <c r="H123" s="16"/>
-      <c r="I123" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J123" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K123" s="16"/>
-    </row>
-    <row r="124" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A124" s="7">
-        <v>121</v>
-      </c>
-      <c r="B124" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="8"/>
-      <c r="G124" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H124" s="8"/>
-      <c r="I124" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J124" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K124" s="8"/>
+      <c r="F124" s="13"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
+      <c r="I124" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="J124" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K124" s="13"/>
     </row>
     <row r="125" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="15">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C125" s="16"/>
       <c r="D125" s="16"/>
       <c r="E125" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F125" s="16"/>
       <c r="G125" s="16"/>
@@ -4126,17 +4184,17 @@
     </row>
     <row r="126" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
       <c r="G126" s="8" t="s">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="H126" s="8"/>
       <c r="I126" s="11" t="s">
@@ -4148,64 +4206,64 @@
       <c r="K126" s="8"/>
     </row>
     <row r="127" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A127" s="7">
-        <v>124</v>
-      </c>
-      <c r="B127" s="8" t="s">
+      <c r="A127" s="15">
+        <v>122</v>
+      </c>
+      <c r="B127" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H127" s="8"/>
-      <c r="I127" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J127" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K127" s="8"/>
+      <c r="C127" s="16"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="F127" s="16"/>
+      <c r="G127" s="16"/>
+      <c r="H127" s="16"/>
+      <c r="I127" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J127" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K127" s="16"/>
     </row>
     <row r="128" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="15">
-        <v>125</v>
-      </c>
-      <c r="B128" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="C128" s="16"/>
-      <c r="D128" s="16"/>
-      <c r="E128" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="F128" s="16"/>
-      <c r="G128" s="16"/>
-      <c r="H128" s="16"/>
-      <c r="I128" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J128" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K128" s="16"/>
+      <c r="A128" s="7">
+        <v>123</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C128" s="8"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H128" s="8"/>
+      <c r="I128" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J128" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K128" s="8"/>
     </row>
     <row r="129" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
       <c r="G129" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H129" s="8"/>
       <c r="I129" s="11" t="s">
@@ -4216,140 +4274,140 @@
       </c>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A130" s="7">
+    <row r="130" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A130" s="15">
+        <v>125</v>
+      </c>
+      <c r="B130" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C130" s="16"/>
+      <c r="D130" s="16"/>
+      <c r="E130" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F130" s="16"/>
+      <c r="G130" s="16"/>
+      <c r="H130" s="16"/>
+      <c r="I130" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J130" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K130" s="16"/>
+    </row>
+    <row r="131" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A131" s="7">
+        <v>126</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="8"/>
+      <c r="G131" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="H131" s="8"/>
+      <c r="I131" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K131" s="8"/>
+    </row>
+    <row r="132" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="7">
         <v>127</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="B132" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
-      <c r="G130" s="8" t="s">
+      <c r="C132" s="8"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+      <c r="G132" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="H130" s="8"/>
-      <c r="I130" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J130" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K130" s="8" t="s">
+      <c r="H132" s="8"/>
+      <c r="I132" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K132" s="8" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A131" s="4">
+    <row r="133" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A133" s="4">
         <v>128</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B133" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C131" s="5" t="s">
+      <c r="C133" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D131" s="5" t="s">
+      <c r="D133" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="5"/>
-      <c r="H131" s="5" t="s">
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I131" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J131" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K131" s="5"/>
-    </row>
-    <row r="132" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="12">
+      <c r="I133" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K133" s="5"/>
+    </row>
+    <row r="134" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="12">
         <v>129</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B134" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="C132" s="13"/>
-      <c r="D132" s="13" t="s">
+      <c r="C134" s="13"/>
+      <c r="D134" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="E132" s="13" t="s">
+      <c r="E134" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="F132" s="13"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
-      <c r="I132" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J132" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K132" s="13"/>
-    </row>
-    <row r="133" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A133" s="15">
-        <v>130</v>
-      </c>
-      <c r="B133" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="C133" s="16"/>
-      <c r="D133" s="16"/>
-      <c r="E133" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="F133" s="16"/>
-      <c r="G133" s="16"/>
-      <c r="H133" s="16"/>
-      <c r="I133" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J133" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K133" s="16"/>
-    </row>
-    <row r="134" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A134" s="7">
-        <v>131</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H134" s="8"/>
-      <c r="I134" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J134" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K134" s="8"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
+      <c r="I134" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J134" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K134" s="13"/>
     </row>
     <row r="135" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="15">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C135" s="16"/>
       <c r="D135" s="16"/>
       <c r="E135" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F135" s="16"/>
       <c r="G135" s="16"/>
@@ -4364,17 +4422,17 @@
     </row>
     <row r="136" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="7">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
       <c r="G136" s="8" t="s">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="H136" s="8"/>
       <c r="I136" s="9" t="s">
@@ -4386,64 +4444,64 @@
       <c r="K136" s="8"/>
     </row>
     <row r="137" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A137" s="7">
-        <v>134</v>
-      </c>
-      <c r="B137" s="8" t="s">
+      <c r="A137" s="15">
+        <v>132</v>
+      </c>
+      <c r="B137" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="H137" s="8"/>
-      <c r="I137" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J137" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K137" s="8"/>
+      <c r="C137" s="16"/>
+      <c r="D137" s="16"/>
+      <c r="E137" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
+      <c r="H137" s="16"/>
+      <c r="I137" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J137" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K137" s="16"/>
     </row>
     <row r="138" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A138" s="15">
-        <v>135</v>
-      </c>
-      <c r="B138" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="C138" s="16"/>
-      <c r="D138" s="16"/>
-      <c r="E138" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="F138" s="16"/>
-      <c r="G138" s="16"/>
-      <c r="H138" s="16"/>
-      <c r="I138" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J138" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K138" s="16"/>
+      <c r="A138" s="7">
+        <v>133</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C138" s="8"/>
+      <c r="D138" s="8"/>
+      <c r="E138" s="8"/>
+      <c r="F138" s="8"/>
+      <c r="G138" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H138" s="8"/>
+      <c r="I138" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K138" s="8"/>
     </row>
     <row r="139" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="7">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
       <c r="G139" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H139" s="8"/>
       <c r="I139" s="9" t="s">
@@ -4452,36 +4510,34 @@
       <c r="J139" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K139" s="8" t="s">
-        <v>203</v>
-      </c>
+      <c r="K139" s="8"/>
     </row>
     <row r="140" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A140" s="7">
-        <v>137</v>
-      </c>
-      <c r="B140" s="8" t="s">
+      <c r="A140" s="15">
+        <v>135</v>
+      </c>
+      <c r="B140" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="H140" s="8"/>
-      <c r="I140" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J140" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K140" s="8"/>
-    </row>
-    <row r="141" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
+      <c r="H140" s="16"/>
+      <c r="I140" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J140" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K140" s="16"/>
+    </row>
+    <row r="141" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="7">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B141" s="8" t="s">
         <v>200</v>
@@ -4491,7 +4547,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
       <c r="G141" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H141" s="8"/>
       <c r="I141" s="9" t="s">
@@ -4500,10 +4556,58 @@
       <c r="J141" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K141" s="8"/>
+      <c r="K141" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="7">
+        <v>137</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C142" s="8"/>
+      <c r="D142" s="8"/>
+      <c r="E142" s="8"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H142" s="8"/>
+      <c r="I142" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K142" s="8"/>
+    </row>
+    <row r="143" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+      <c r="A143" s="7">
+        <v>138</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C143" s="8"/>
+      <c r="D143" s="8"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8"/>
+      <c r="G143" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H143" s="8"/>
+      <c r="I143" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K143" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K140" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:K142" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>

--- a/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C34BFD-2D4B-4ED0-9F8B-A75D204BEED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5DED77-9959-42C2-828E-27E0E193AE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="215">
   <si>
     <t>ソフトウェア仕様書 WBS（Work Breakdown Structure）</t>
   </si>
@@ -1763,8 +1763,8 @@
       <c r="A23" s="7">
         <v>20</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>39</v>
+      <c r="B23" s="8">
+        <v>2.1</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -1788,8 +1788,8 @@
       <c r="A24" s="7">
         <v>21</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>39</v>
+      <c r="B24" s="8">
+        <v>2.2000000000000002</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -1813,8 +1813,8 @@
       <c r="A25" s="7">
         <v>22</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>39</v>
+      <c r="B25" s="8">
+        <v>2.2999999999999998</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -1838,8 +1838,8 @@
       <c r="A26" s="7">
         <v>23</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>39</v>
+      <c r="B26" s="8">
+        <v>2.4</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -1863,8 +1863,8 @@
       <c r="A27" s="7">
         <v>24</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>39</v>
+      <c r="B27" s="8">
+        <v>2.5</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -1888,8 +1888,8 @@
       <c r="A28" s="7">
         <v>25</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>39</v>
+      <c r="B28" s="8">
+        <v>2.6</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -1913,8 +1913,8 @@
       <c r="A29" s="7">
         <v>26</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>39</v>
+      <c r="B29" s="8">
+        <v>2.7</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>

--- a/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\soruce\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5DED77-9959-42C2-828E-27E0E193AE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75EAECC-8A0D-4337-9AF8-0CEC527A8A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="216">
   <si>
     <t>ソフトウェア仕様書 WBS（Work Breakdown Structure）</t>
   </si>
@@ -708,6 +708,13 @@
     <t>赤木</t>
     <rPh sb="0" eb="2">
       <t>アカギ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -1242,22 +1249,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K143"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1272,8 +1279,8 @@
       <c r="J1" s="22"/>
       <c r="K1" s="22"/>
     </row>
-    <row r="2" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="3" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1308,7 +1315,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1327,7 +1334,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1354,7 +1361,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -1377,7 +1384,7 @@
       </c>
       <c r="K6" s="8"/>
     </row>
-    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1400,7 +1407,7 @@
       </c>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1423,7 +1430,7 @@
       </c>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1450,7 +1457,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -1473,7 +1480,7 @@
       </c>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -1496,7 +1503,7 @@
       </c>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -1519,7 +1526,7 @@
       </c>
       <c r="K12" s="8"/>
     </row>
-    <row r="13" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -1546,7 +1553,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>11</v>
       </c>
@@ -1569,7 +1576,7 @@
       </c>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>12</v>
       </c>
@@ -1592,7 +1599,7 @@
       </c>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -1619,7 +1626,7 @@
       </c>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -1642,7 +1649,7 @@
       </c>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>15</v>
       </c>
@@ -1665,7 +1672,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -1692,7 +1699,7 @@
       </c>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>17</v>
       </c>
@@ -1715,7 +1722,7 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>18</v>
       </c>
@@ -1738,7 +1745,7 @@
       </c>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1759,7 +1766,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>20</v>
       </c>
@@ -1780,11 +1787,11 @@
         <v>16</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>21</v>
       </c>
@@ -1809,7 +1816,7 @@
       </c>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>22</v>
       </c>
@@ -1830,11 +1837,11 @@
         <v>16</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>23</v>
       </c>
@@ -1855,11 +1862,11 @@
         <v>28</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>24</v>
       </c>
@@ -1884,7 +1891,7 @@
       </c>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>25</v>
       </c>
@@ -1909,7 +1916,7 @@
       </c>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>26</v>
       </c>
@@ -1934,7 +1941,7 @@
       </c>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>25</v>
       </c>
@@ -1953,7 +1960,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>26</v>
       </c>
@@ -1980,7 +1987,7 @@
       </c>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>27</v>
       </c>
@@ -2005,7 +2012,7 @@
       </c>
       <c r="K32" s="13"/>
     </row>
-    <row r="33" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
         <v>28</v>
       </c>
@@ -2028,7 +2035,7 @@
       </c>
       <c r="K33" s="16"/>
     </row>
-    <row r="34" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>29</v>
       </c>
@@ -2051,7 +2058,7 @@
       </c>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>30</v>
       </c>
@@ -2074,7 +2081,7 @@
       </c>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
         <v>31</v>
       </c>
@@ -2097,7 +2104,7 @@
       </c>
       <c r="K36" s="16"/>
     </row>
-    <row r="37" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>32</v>
       </c>
@@ -2120,7 +2127,7 @@
       </c>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>33</v>
       </c>
@@ -2143,7 +2150,7 @@
       </c>
       <c r="K38" s="8"/>
     </row>
-    <row r="39" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>34</v>
       </c>
@@ -2166,7 +2173,7 @@
       </c>
       <c r="K39" s="8"/>
     </row>
-    <row r="40" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="15">
         <v>35</v>
       </c>
@@ -2189,7 +2196,7 @@
       </c>
       <c r="K40" s="16"/>
     </row>
-    <row r="41" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>36</v>
       </c>
@@ -2212,7 +2219,7 @@
       </c>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>37</v>
       </c>
@@ -2235,7 +2242,7 @@
       </c>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>38</v>
       </c>
@@ -2258,7 +2265,7 @@
       </c>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>39</v>
       </c>
@@ -2283,7 +2290,7 @@
       </c>
       <c r="K44" s="13"/>
     </row>
-    <row r="45" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="15">
         <v>40</v>
       </c>
@@ -2306,7 +2313,7 @@
       </c>
       <c r="K45" s="16"/>
     </row>
-    <row r="46" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>41</v>
       </c>
@@ -2329,7 +2336,7 @@
       </c>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>42</v>
       </c>
@@ -2352,7 +2359,7 @@
       </c>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15">
         <v>43</v>
       </c>
@@ -2375,7 +2382,7 @@
       </c>
       <c r="K48" s="16"/>
     </row>
-    <row r="49" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>44</v>
       </c>
@@ -2398,7 +2405,7 @@
       </c>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>45</v>
       </c>
@@ -2421,7 +2428,7 @@
       </c>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>46</v>
       </c>
@@ -2444,7 +2451,7 @@
       </c>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="15">
         <v>47</v>
       </c>
@@ -2467,7 +2474,7 @@
       </c>
       <c r="K52" s="16"/>
     </row>
-    <row r="53" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>48</v>
       </c>
@@ -2490,7 +2497,7 @@
       </c>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>49</v>
       </c>
@@ -2513,7 +2520,7 @@
       </c>
       <c r="K54" s="8"/>
     </row>
-    <row r="55" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>50</v>
       </c>
@@ -2536,7 +2543,7 @@
       </c>
       <c r="K55" s="8"/>
     </row>
-    <row r="56" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>51</v>
       </c>
@@ -2561,7 +2568,7 @@
       </c>
       <c r="K56" s="13"/>
     </row>
-    <row r="57" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="15">
         <v>52</v>
       </c>
@@ -2584,7 +2591,7 @@
       </c>
       <c r="K57" s="16"/>
     </row>
-    <row r="58" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>53</v>
       </c>
@@ -2607,7 +2614,7 @@
       </c>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="15">
         <v>54</v>
       </c>
@@ -2630,7 +2637,7 @@
       </c>
       <c r="K59" s="16"/>
     </row>
-    <row r="60" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>55</v>
       </c>
@@ -2653,7 +2660,7 @@
       </c>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>56</v>
       </c>
@@ -2676,7 +2683,7 @@
       </c>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="15">
         <v>57</v>
       </c>
@@ -2699,7 +2706,7 @@
       </c>
       <c r="K62" s="16"/>
     </row>
-    <row r="63" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>58</v>
       </c>
@@ -2722,7 +2729,7 @@
       </c>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>59</v>
       </c>
@@ -2745,7 +2752,7 @@
       </c>
       <c r="K64" s="8"/>
     </row>
-    <row r="65" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>60</v>
       </c>
@@ -2772,7 +2779,7 @@
       </c>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>61</v>
       </c>
@@ -2797,7 +2804,7 @@
       </c>
       <c r="K66" s="13"/>
     </row>
-    <row r="67" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="15">
         <v>62</v>
       </c>
@@ -2820,7 +2827,7 @@
       </c>
       <c r="K67" s="16"/>
     </row>
-    <row r="68" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>63</v>
       </c>
@@ -2843,7 +2850,7 @@
       </c>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="15">
         <v>64</v>
       </c>
@@ -2866,7 +2873,7 @@
       </c>
       <c r="K69" s="16"/>
     </row>
-    <row r="70" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>65</v>
       </c>
@@ -2889,7 +2896,7 @@
       </c>
       <c r="K70" s="8"/>
     </row>
-    <row r="71" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>66</v>
       </c>
@@ -2912,7 +2919,7 @@
       </c>
       <c r="K71" s="8"/>
     </row>
-    <row r="72" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>67</v>
       </c>
@@ -2935,7 +2942,7 @@
       </c>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="15">
         <v>68</v>
       </c>
@@ -2958,7 +2965,7 @@
       </c>
       <c r="K73" s="16"/>
     </row>
-    <row r="74" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>69</v>
       </c>
@@ -2981,7 +2988,7 @@
       </c>
       <c r="K74" s="8"/>
     </row>
-    <row r="75" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>70</v>
       </c>
@@ -3004,7 +3011,7 @@
       </c>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>71</v>
       </c>
@@ -3029,7 +3036,7 @@
       </c>
       <c r="K76" s="13"/>
     </row>
-    <row r="77" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="15">
         <v>72</v>
       </c>
@@ -3052,7 +3059,7 @@
       </c>
       <c r="K77" s="16"/>
     </row>
-    <row r="78" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>73</v>
       </c>
@@ -3075,7 +3082,7 @@
       </c>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="15">
         <v>74</v>
       </c>
@@ -3098,7 +3105,7 @@
       </c>
       <c r="K79" s="16"/>
     </row>
-    <row r="80" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>75</v>
       </c>
@@ -3121,7 +3128,7 @@
       </c>
       <c r="K80" s="8"/>
     </row>
-    <row r="81" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>76</v>
       </c>
@@ -3144,7 +3151,7 @@
       </c>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>77</v>
       </c>
@@ -3167,7 +3174,7 @@
       </c>
       <c r="K82" s="8"/>
     </row>
-    <row r="83" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="15">
         <v>78</v>
       </c>
@@ -3190,7 +3197,7 @@
       </c>
       <c r="K83" s="16"/>
     </row>
-    <row r="84" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>79</v>
       </c>
@@ -3213,7 +3220,7 @@
       </c>
       <c r="K84" s="8"/>
     </row>
-    <row r="85" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>80</v>
       </c>
@@ -3236,7 +3243,7 @@
       </c>
       <c r="K85" s="8"/>
     </row>
-    <row r="86" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>81</v>
       </c>
@@ -3259,7 +3266,7 @@
       </c>
       <c r="K86" s="8"/>
     </row>
-    <row r="87" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>82</v>
       </c>
@@ -3284,7 +3291,7 @@
       </c>
       <c r="K87" s="13"/>
     </row>
-    <row r="88" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="15">
         <v>83</v>
       </c>
@@ -3307,7 +3314,7 @@
       </c>
       <c r="K88" s="16"/>
     </row>
-    <row r="89" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>84</v>
       </c>
@@ -3330,7 +3337,7 @@
       </c>
       <c r="K89" s="8"/>
     </row>
-    <row r="90" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="15">
         <v>85</v>
       </c>
@@ -3353,7 +3360,7 @@
       </c>
       <c r="K90" s="16"/>
     </row>
-    <row r="91" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>86</v>
       </c>
@@ -3376,7 +3383,7 @@
       </c>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="15">
         <v>87</v>
       </c>
@@ -3399,7 +3406,7 @@
       </c>
       <c r="K92" s="16"/>
     </row>
-    <row r="93" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7">
         <v>88</v>
       </c>
@@ -3422,7 +3429,7 @@
       </c>
       <c r="K93" s="8"/>
     </row>
-    <row r="94" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>89</v>
       </c>
@@ -3445,7 +3452,7 @@
       </c>
       <c r="K94" s="8"/>
     </row>
-    <row r="95" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>90</v>
       </c>
@@ -3472,7 +3479,7 @@
       </c>
       <c r="K95" s="5"/>
     </row>
-    <row r="96" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>91</v>
       </c>
@@ -3497,7 +3504,7 @@
       </c>
       <c r="K96" s="13"/>
     </row>
-    <row r="97" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="15">
         <v>92</v>
       </c>
@@ -3520,7 +3527,7 @@
       </c>
       <c r="K97" s="16"/>
     </row>
-    <row r="98" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <v>93</v>
       </c>
@@ -3543,7 +3550,7 @@
       </c>
       <c r="K98" s="8"/>
     </row>
-    <row r="99" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="15">
         <v>94</v>
       </c>
@@ -3566,7 +3573,7 @@
       </c>
       <c r="K99" s="16"/>
     </row>
-    <row r="100" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <v>95</v>
       </c>
@@ -3589,7 +3596,7 @@
       </c>
       <c r="K100" s="8"/>
     </row>
-    <row r="101" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <v>96</v>
       </c>
@@ -3612,7 +3619,7 @@
       </c>
       <c r="K101" s="8"/>
     </row>
-    <row r="102" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="15">
         <v>97</v>
       </c>
@@ -3635,7 +3642,7 @@
       </c>
       <c r="K102" s="16"/>
     </row>
-    <row r="103" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <v>98</v>
       </c>
@@ -3658,7 +3665,7 @@
       </c>
       <c r="K103" s="8"/>
     </row>
-    <row r="104" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <v>99</v>
       </c>
@@ -3683,7 +3690,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>100</v>
       </c>
@@ -3708,7 +3715,7 @@
       </c>
       <c r="K105" s="13"/>
     </row>
-    <row r="106" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="15">
         <v>101</v>
       </c>
@@ -3731,7 +3738,7 @@
       </c>
       <c r="K106" s="16"/>
     </row>
-    <row r="107" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <v>102</v>
       </c>
@@ -3754,7 +3761,7 @@
       </c>
       <c r="K107" s="8"/>
     </row>
-    <row r="108" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="15">
         <v>103</v>
       </c>
@@ -3777,7 +3784,7 @@
       </c>
       <c r="K108" s="16"/>
     </row>
-    <row r="109" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <v>104</v>
       </c>
@@ -3800,7 +3807,7 @@
       </c>
       <c r="K109" s="8"/>
     </row>
-    <row r="110" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <v>105</v>
       </c>
@@ -3823,7 +3830,7 @@
       </c>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="15">
         <v>106</v>
       </c>
@@ -3846,7 +3853,7 @@
       </c>
       <c r="K111" s="16"/>
     </row>
-    <row r="112" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <v>107</v>
       </c>
@@ -3869,7 +3876,7 @@
       </c>
       <c r="K112" s="8"/>
     </row>
-    <row r="113" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="7">
         <v>108</v>
       </c>
@@ -3892,7 +3899,7 @@
       </c>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>109</v>
       </c>
@@ -3919,7 +3926,7 @@
       </c>
       <c r="K114" s="5"/>
     </row>
-    <row r="115" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>110</v>
       </c>
@@ -3944,7 +3951,7 @@
       </c>
       <c r="K115" s="13"/>
     </row>
-    <row r="116" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15">
         <v>111</v>
       </c>
@@ -3967,7 +3974,7 @@
       </c>
       <c r="K116" s="16"/>
     </row>
-    <row r="117" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="7">
         <v>112</v>
       </c>
@@ -3990,7 +3997,7 @@
       </c>
       <c r="K117" s="8"/>
     </row>
-    <row r="118" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15">
         <v>113</v>
       </c>
@@ -4013,7 +4020,7 @@
       </c>
       <c r="K118" s="16"/>
     </row>
-    <row r="119" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="7">
         <v>114</v>
       </c>
@@ -4036,7 +4043,7 @@
       </c>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15">
         <v>115</v>
       </c>
@@ -4059,7 +4066,7 @@
       </c>
       <c r="K120" s="16"/>
     </row>
-    <row r="121" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="7">
         <v>116</v>
       </c>
@@ -4082,7 +4089,7 @@
       </c>
       <c r="K121" s="8"/>
     </row>
-    <row r="122" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <v>117</v>
       </c>
@@ -4107,7 +4114,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>118</v>
       </c>
@@ -4134,7 +4141,7 @@
       </c>
       <c r="K123" s="5"/>
     </row>
-    <row r="124" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>119</v>
       </c>
@@ -4159,7 +4166,7 @@
       </c>
       <c r="K124" s="13"/>
     </row>
-    <row r="125" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15">
         <v>120</v>
       </c>
@@ -4182,7 +4189,7 @@
       </c>
       <c r="K125" s="16"/>
     </row>
-    <row r="126" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <v>121</v>
       </c>
@@ -4205,7 +4212,7 @@
       </c>
       <c r="K126" s="8"/>
     </row>
-    <row r="127" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15">
         <v>122</v>
       </c>
@@ -4228,7 +4235,7 @@
       </c>
       <c r="K127" s="16"/>
     </row>
-    <row r="128" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <v>123</v>
       </c>
@@ -4251,7 +4258,7 @@
       </c>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <v>124</v>
       </c>
@@ -4274,7 +4281,7 @@
       </c>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="15">
         <v>125</v>
       </c>
@@ -4297,7 +4304,7 @@
       </c>
       <c r="K130" s="16"/>
     </row>
-    <row r="131" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <v>126</v>
       </c>
@@ -4320,7 +4327,7 @@
       </c>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <v>127</v>
       </c>
@@ -4345,7 +4352,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>128</v>
       </c>
@@ -4372,7 +4379,7 @@
       </c>
       <c r="K133" s="5"/>
     </row>
-    <row r="134" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>129</v>
       </c>
@@ -4397,7 +4404,7 @@
       </c>
       <c r="K134" s="13"/>
     </row>
-    <row r="135" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="15">
         <v>130</v>
       </c>
@@ -4420,7 +4427,7 @@
       </c>
       <c r="K135" s="16"/>
     </row>
-    <row r="136" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <v>131</v>
       </c>
@@ -4443,7 +4450,7 @@
       </c>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="15">
         <v>132</v>
       </c>
@@ -4466,7 +4473,7 @@
       </c>
       <c r="K137" s="16"/>
     </row>
-    <row r="138" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <v>133</v>
       </c>
@@ -4489,7 +4496,7 @@
       </c>
       <c r="K138" s="8"/>
     </row>
-    <row r="139" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="7">
         <v>134</v>
       </c>
@@ -4512,7 +4519,7 @@
       </c>
       <c r="K139" s="8"/>
     </row>
-    <row r="140" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="15">
         <v>135</v>
       </c>
@@ -4535,7 +4542,7 @@
       </c>
       <c r="K140" s="16"/>
     </row>
-    <row r="141" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="7">
         <v>136</v>
       </c>
@@ -4560,7 +4567,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="7">
         <v>137</v>
       </c>
@@ -4583,7 +4590,7 @@
       </c>
       <c r="K142" s="8"/>
     </row>
-    <row r="143" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:11" ht="14.5" x14ac:dyDescent="0.2">
       <c r="A143" s="7">
         <v>138</v>
       </c>

--- a/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\soruce\DOC\基本設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75EAECC-8A0D-4337-9AF8-0CEC527A8A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA79533-DBB1-4A14-B5E2-387F7D3260AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1249,22 +1249,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K143"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1279,8 +1279,8 @@
       <c r="J1" s="22"/>
       <c r="K1" s="22"/>
     </row>
-    <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="3" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="K6" s="8"/>
     </row>
-    <row r="7" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7">
         <v>4</v>
       </c>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7">
         <v>5</v>
       </c>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7">
         <v>7</v>
       </c>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7">
         <v>8</v>
       </c>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="K11" s="8"/>
     </row>
-    <row r="12" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7">
         <v>9</v>
       </c>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="K12" s="8"/>
     </row>
-    <row r="13" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7">
         <v>11</v>
       </c>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7">
         <v>12</v>
       </c>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7">
         <v>14</v>
       </c>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
         <v>15</v>
       </c>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7">
         <v>17</v>
       </c>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7">
         <v>18</v>
       </c>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -1766,7 +1766,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="7">
         <v>20</v>
       </c>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="7">
         <v>21</v>
       </c>
@@ -1812,11 +1812,11 @@
         <v>16</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="7">
         <v>22</v>
       </c>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="7">
         <v>23</v>
       </c>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="7">
         <v>24</v>
       </c>
@@ -1887,11 +1887,11 @@
         <v>28</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K27" s="8"/>
     </row>
-    <row r="28" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="7">
         <v>25</v>
       </c>
@@ -1912,11 +1912,11 @@
         <v>28</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K28" s="8"/>
     </row>
-    <row r="29" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="7">
         <v>26</v>
       </c>
@@ -1931,17 +1931,17 @@
         <v>212</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>28</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
         <v>25</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
         <v>26</v>
       </c>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="12">
         <v>27</v>
       </c>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="K32" s="13"/>
     </row>
-    <row r="33" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="15">
         <v>28</v>
       </c>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="K33" s="16"/>
     </row>
-    <row r="34" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7">
         <v>29</v>
       </c>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7">
         <v>30</v>
       </c>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="15">
         <v>31</v>
       </c>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="K36" s="16"/>
     </row>
-    <row r="37" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7">
         <v>32</v>
       </c>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7">
         <v>33</v>
       </c>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="K38" s="8"/>
     </row>
-    <row r="39" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7">
         <v>34</v>
       </c>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="K39" s="8"/>
     </row>
-    <row r="40" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="15">
         <v>35</v>
       </c>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="K40" s="16"/>
     </row>
-    <row r="41" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7">
         <v>36</v>
       </c>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7">
         <v>37</v>
       </c>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7">
         <v>38</v>
       </c>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="12">
         <v>39</v>
       </c>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K44" s="13"/>
     </row>
-    <row r="45" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="15">
         <v>40</v>
       </c>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="K45" s="16"/>
     </row>
-    <row r="46" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
         <v>41</v>
       </c>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7">
         <v>42</v>
       </c>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="15">
         <v>43</v>
       </c>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="K48" s="16"/>
     </row>
-    <row r="49" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7">
         <v>44</v>
       </c>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="7">
         <v>45</v>
       </c>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="7">
         <v>46</v>
       </c>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="15">
         <v>47</v>
       </c>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="K52" s="16"/>
     </row>
-    <row r="53" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="7">
         <v>48</v>
       </c>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="7">
         <v>49</v>
       </c>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="K54" s="8"/>
     </row>
-    <row r="55" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="7">
         <v>50</v>
       </c>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="K55" s="8"/>
     </row>
-    <row r="56" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="12">
         <v>51</v>
       </c>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="K56" s="13"/>
     </row>
-    <row r="57" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="15">
         <v>52</v>
       </c>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="K57" s="16"/>
     </row>
-    <row r="58" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="7">
         <v>53</v>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="15">
         <v>54</v>
       </c>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="K59" s="16"/>
     </row>
-    <row r="60" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
         <v>55</v>
       </c>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="7">
         <v>56</v>
       </c>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="15">
         <v>57</v>
       </c>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K62" s="16"/>
     </row>
-    <row r="63" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="7">
         <v>58</v>
       </c>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="7">
         <v>59</v>
       </c>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="K64" s="8"/>
     </row>
-    <row r="65" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="4">
         <v>60</v>
       </c>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="12">
         <v>61</v>
       </c>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="K66" s="13"/>
     </row>
-    <row r="67" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="15">
         <v>62</v>
       </c>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="K67" s="16"/>
     </row>
-    <row r="68" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="7">
         <v>63</v>
       </c>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
         <v>64</v>
       </c>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K69" s="16"/>
     </row>
-    <row r="70" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="7">
         <v>65</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="K70" s="8"/>
     </row>
-    <row r="71" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="7">
         <v>66</v>
       </c>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K71" s="8"/>
     </row>
-    <row r="72" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="7">
         <v>67</v>
       </c>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="15">
         <v>68</v>
       </c>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="K73" s="16"/>
     </row>
-    <row r="74" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="7">
         <v>69</v>
       </c>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="K74" s="8"/>
     </row>
-    <row r="75" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="7">
         <v>70</v>
       </c>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="12">
         <v>71</v>
       </c>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="K76" s="13"/>
     </row>
-    <row r="77" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="15">
         <v>72</v>
       </c>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K77" s="16"/>
     </row>
-    <row r="78" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="7">
         <v>73</v>
       </c>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="15">
         <v>74</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="K79" s="16"/>
     </row>
-    <row r="80" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="7">
         <v>75</v>
       </c>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="K80" s="8"/>
     </row>
-    <row r="81" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="7">
         <v>76</v>
       </c>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="7">
         <v>77</v>
       </c>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K82" s="8"/>
     </row>
-    <row r="83" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="15">
         <v>78</v>
       </c>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="K83" s="16"/>
     </row>
-    <row r="84" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="7">
         <v>79</v>
       </c>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="K84" s="8"/>
     </row>
-    <row r="85" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="7">
         <v>80</v>
       </c>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K85" s="8"/>
     </row>
-    <row r="86" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="7">
         <v>81</v>
       </c>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="K86" s="8"/>
     </row>
-    <row r="87" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="12">
         <v>82</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="K87" s="13"/>
     </row>
-    <row r="88" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
         <v>83</v>
       </c>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="K88" s="16"/>
     </row>
-    <row r="89" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="7">
         <v>84</v>
       </c>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="K89" s="8"/>
     </row>
-    <row r="90" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="15">
         <v>85</v>
       </c>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="K90" s="16"/>
     </row>
-    <row r="91" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="7">
         <v>86</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="15">
         <v>87</v>
       </c>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K92" s="16"/>
     </row>
-    <row r="93" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="7">
         <v>88</v>
       </c>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="K93" s="8"/>
     </row>
-    <row r="94" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="7">
         <v>89</v>
       </c>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="K94" s="8"/>
     </row>
-    <row r="95" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="4">
         <v>90</v>
       </c>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="K95" s="5"/>
     </row>
-    <row r="96" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="12">
         <v>91</v>
       </c>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="K96" s="13"/>
     </row>
-    <row r="97" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="15">
         <v>92</v>
       </c>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="K97" s="16"/>
     </row>
-    <row r="98" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="7">
         <v>93</v>
       </c>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="K98" s="8"/>
     </row>
-    <row r="99" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="15">
         <v>94</v>
       </c>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="K99" s="16"/>
     </row>
-    <row r="100" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="7">
         <v>95</v>
       </c>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="K100" s="8"/>
     </row>
-    <row r="101" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="7">
         <v>96</v>
       </c>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="K101" s="8"/>
     </row>
-    <row r="102" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="15">
         <v>97</v>
       </c>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K102" s="16"/>
     </row>
-    <row r="103" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="7">
         <v>98</v>
       </c>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="K103" s="8"/>
     </row>
-    <row r="104" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="7">
         <v>99</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="12">
         <v>100</v>
       </c>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="K105" s="13"/>
     </row>
-    <row r="106" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="15">
         <v>101</v>
       </c>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="K106" s="16"/>
     </row>
-    <row r="107" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="7">
         <v>102</v>
       </c>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K107" s="8"/>
     </row>
-    <row r="108" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="15">
         <v>103</v>
       </c>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="K108" s="16"/>
     </row>
-    <row r="109" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="7">
         <v>104</v>
       </c>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="K109" s="8"/>
     </row>
-    <row r="110" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="7">
         <v>105</v>
       </c>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="15">
         <v>106</v>
       </c>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="K111" s="16"/>
     </row>
-    <row r="112" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="7">
         <v>107</v>
       </c>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="K112" s="8"/>
     </row>
-    <row r="113" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="7">
         <v>108</v>
       </c>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="4">
         <v>109</v>
       </c>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="K114" s="5"/>
     </row>
-    <row r="115" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="12">
         <v>110</v>
       </c>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="K115" s="13"/>
     </row>
-    <row r="116" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="15">
         <v>111</v>
       </c>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="K116" s="16"/>
     </row>
-    <row r="117" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="7">
         <v>112</v>
       </c>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="K117" s="8"/>
     </row>
-    <row r="118" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="15">
         <v>113</v>
       </c>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="K118" s="16"/>
     </row>
-    <row r="119" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="7">
         <v>114</v>
       </c>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="15">
         <v>115</v>
       </c>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="K120" s="16"/>
     </row>
-    <row r="121" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="7">
         <v>116</v>
       </c>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="K121" s="8"/>
     </row>
-    <row r="122" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="7">
         <v>117</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="4">
         <v>118</v>
       </c>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="K123" s="5"/>
     </row>
-    <row r="124" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="12">
         <v>119</v>
       </c>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="K124" s="13"/>
     </row>
-    <row r="125" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="15">
         <v>120</v>
       </c>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K125" s="16"/>
     </row>
-    <row r="126" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="7">
         <v>121</v>
       </c>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K126" s="8"/>
     </row>
-    <row r="127" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="15">
         <v>122</v>
       </c>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="K127" s="16"/>
     </row>
-    <row r="128" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="7">
         <v>123</v>
       </c>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="7">
         <v>124</v>
       </c>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="15">
         <v>125</v>
       </c>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="K130" s="16"/>
     </row>
-    <row r="131" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="7">
         <v>126</v>
       </c>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="7">
         <v>127</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="4">
         <v>128</v>
       </c>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="K133" s="5"/>
     </row>
-    <row r="134" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="12">
         <v>129</v>
       </c>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="K134" s="13"/>
     </row>
-    <row r="135" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="15">
         <v>130</v>
       </c>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="K135" s="16"/>
     </row>
-    <row r="136" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="7">
         <v>131</v>
       </c>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="15">
         <v>132</v>
       </c>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="K137" s="16"/>
     </row>
-    <row r="138" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="7">
         <v>133</v>
       </c>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="K138" s="8"/>
     </row>
-    <row r="139" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="7">
         <v>134</v>
       </c>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="K139" s="8"/>
     </row>
-    <row r="140" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="15">
         <v>135</v>
       </c>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="K140" s="16"/>
     </row>
-    <row r="141" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="7">
         <v>136</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="7">
         <v>137</v>
       </c>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="K142" s="8"/>
     </row>
-    <row r="143" spans="1:11" ht="14.5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" ht="15" x14ac:dyDescent="0.15">
       <c r="A143" s="7">
         <v>138</v>
       </c>

--- a/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA79533-DBB1-4A14-B5E2-387F7D3260AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A4A1DD-553C-41A5-874B-9E5F107CB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="218">
   <si>
     <t>ソフトウェア仕様書 WBS（Work Breakdown Structure）</t>
   </si>
@@ -708,6 +708,20 @@
     <t>赤木</t>
     <rPh sb="0" eb="2">
       <t>アカギ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>着手中</t>
+    <rPh sb="0" eb="3">
+      <t>チャクシュチュウ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
@@ -1248,15 +1262,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K143"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:K144"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="9.875" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="36.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.625" bestFit="1" customWidth="1"/>
@@ -1983,11 +1997,11 @@
         <v>16</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A32" s="12">
         <v>27</v>
       </c>
@@ -2008,11 +2022,11 @@
         <v>16</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="K32" s="13"/>
     </row>
-    <row r="33" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A33" s="15">
         <v>28</v>
       </c>
@@ -2031,11 +2045,11 @@
         <v>16</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c r="K33" s="16"/>
     </row>
-    <row r="34" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A34" s="7">
         <v>29</v>
       </c>
@@ -2054,11 +2068,11 @@
         <v>16</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A35" s="7">
         <v>30</v>
       </c>
@@ -2077,11 +2091,11 @@
         <v>16</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="K35" s="8"/>
     </row>
-    <row r="36" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A36" s="15">
         <v>31</v>
       </c>
@@ -2104,7 +2118,7 @@
       </c>
       <c r="K36" s="16"/>
     </row>
-    <row r="37" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A37" s="7">
         <v>32</v>
       </c>
@@ -2127,7 +2141,7 @@
       </c>
       <c r="K37" s="8"/>
     </row>
-    <row r="38" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7">
         <v>33</v>
       </c>
@@ -2150,7 +2164,7 @@
       </c>
       <c r="K38" s="8"/>
     </row>
-    <row r="39" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A39" s="7">
         <v>34</v>
       </c>
@@ -2173,7 +2187,7 @@
       </c>
       <c r="K39" s="8"/>
     </row>
-    <row r="40" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A40" s="15">
         <v>35</v>
       </c>
@@ -2196,7 +2210,7 @@
       </c>
       <c r="K40" s="16"/>
     </row>
-    <row r="41" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A41" s="7">
         <v>36</v>
       </c>
@@ -2219,7 +2233,7 @@
       </c>
       <c r="K41" s="8"/>
     </row>
-    <row r="42" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A42" s="7">
         <v>37</v>
       </c>
@@ -2242,7 +2256,7 @@
       </c>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A43" s="7">
         <v>38</v>
       </c>
@@ -2265,7 +2279,7 @@
       </c>
       <c r="K43" s="8"/>
     </row>
-    <row r="44" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A44" s="12">
         <v>39</v>
       </c>
@@ -2290,7 +2304,7 @@
       </c>
       <c r="K44" s="13"/>
     </row>
-    <row r="45" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A45" s="15">
         <v>40</v>
       </c>
@@ -2313,7 +2327,7 @@
       </c>
       <c r="K45" s="16"/>
     </row>
-    <row r="46" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
         <v>41</v>
       </c>
@@ -2336,7 +2350,7 @@
       </c>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A47" s="7">
         <v>42</v>
       </c>
@@ -2359,7 +2373,7 @@
       </c>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A48" s="15">
         <v>43</v>
       </c>
@@ -2382,7 +2396,7 @@
       </c>
       <c r="K48" s="16"/>
     </row>
-    <row r="49" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A49" s="7">
         <v>44</v>
       </c>
@@ -2405,7 +2419,7 @@
       </c>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A50" s="7">
         <v>45</v>
       </c>
@@ -2428,7 +2442,7 @@
       </c>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A51" s="7">
         <v>46</v>
       </c>
@@ -2451,7 +2465,7 @@
       </c>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A52" s="15">
         <v>47</v>
       </c>
@@ -2474,7 +2488,7 @@
       </c>
       <c r="K52" s="16"/>
     </row>
-    <row r="53" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A53" s="7">
         <v>48</v>
       </c>
@@ -2497,7 +2511,7 @@
       </c>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A54" s="7">
         <v>49</v>
       </c>
@@ -2520,7 +2534,7 @@
       </c>
       <c r="K54" s="8"/>
     </row>
-    <row r="55" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A55" s="7">
         <v>50</v>
       </c>
@@ -2543,7 +2557,7 @@
       </c>
       <c r="K55" s="8"/>
     </row>
-    <row r="56" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A56" s="12">
         <v>51</v>
       </c>
@@ -2568,7 +2582,7 @@
       </c>
       <c r="K56" s="13"/>
     </row>
-    <row r="57" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A57" s="15">
         <v>52</v>
       </c>
@@ -2591,7 +2605,7 @@
       </c>
       <c r="K57" s="16"/>
     </row>
-    <row r="58" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A58" s="7">
         <v>53</v>
       </c>
@@ -2614,7 +2628,7 @@
       </c>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A59" s="15">
         <v>54</v>
       </c>
@@ -2637,7 +2651,7 @@
       </c>
       <c r="K59" s="16"/>
     </row>
-    <row r="60" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
         <v>55</v>
       </c>
@@ -2660,7 +2674,7 @@
       </c>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A61" s="7">
         <v>56</v>
       </c>
@@ -2683,7 +2697,7 @@
       </c>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A62" s="15">
         <v>57</v>
       </c>
@@ -2706,7 +2720,7 @@
       </c>
       <c r="K62" s="16"/>
     </row>
-    <row r="63" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A63" s="7">
         <v>58</v>
       </c>
@@ -2729,7 +2743,7 @@
       </c>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:11" ht="15.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A64" s="7">
         <v>59</v>
       </c>
@@ -2779,7 +2793,7 @@
       </c>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A66" s="12">
         <v>61</v>
       </c>
@@ -2804,7 +2818,7 @@
       </c>
       <c r="K66" s="13"/>
     </row>
-    <row r="67" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A67" s="15">
         <v>62</v>
       </c>
@@ -2827,7 +2841,7 @@
       </c>
       <c r="K67" s="16"/>
     </row>
-    <row r="68" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A68" s="7">
         <v>63</v>
       </c>
@@ -2850,7 +2864,7 @@
       </c>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
         <v>64</v>
       </c>
@@ -2873,7 +2887,7 @@
       </c>
       <c r="K69" s="16"/>
     </row>
-    <row r="70" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A70" s="7">
         <v>65</v>
       </c>
@@ -2896,7 +2910,7 @@
       </c>
       <c r="K70" s="8"/>
     </row>
-    <row r="71" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A71" s="7">
         <v>66</v>
       </c>
@@ -2919,7 +2933,7 @@
       </c>
       <c r="K71" s="8"/>
     </row>
-    <row r="72" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A72" s="7">
         <v>67</v>
       </c>
@@ -2942,7 +2956,7 @@
       </c>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A73" s="15">
         <v>68</v>
       </c>
@@ -2965,7 +2979,7 @@
       </c>
       <c r="K73" s="16"/>
     </row>
-    <row r="74" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A74" s="7">
         <v>69</v>
       </c>
@@ -2988,7 +3002,7 @@
       </c>
       <c r="K74" s="8"/>
     </row>
-    <row r="75" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A75" s="7">
         <v>70</v>
       </c>
@@ -3011,7 +3025,7 @@
       </c>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A76" s="12">
         <v>71</v>
       </c>
@@ -3036,7 +3050,7 @@
       </c>
       <c r="K76" s="13"/>
     </row>
-    <row r="77" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A77" s="15">
         <v>72</v>
       </c>
@@ -3059,7 +3073,7 @@
       </c>
       <c r="K77" s="16"/>
     </row>
-    <row r="78" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A78" s="7">
         <v>73</v>
       </c>
@@ -3082,7 +3096,7 @@
       </c>
       <c r="K78" s="8"/>
     </row>
-    <row r="79" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A79" s="15">
         <v>74</v>
       </c>
@@ -3105,7 +3119,7 @@
       </c>
       <c r="K79" s="16"/>
     </row>
-    <row r="80" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A80" s="7">
         <v>75</v>
       </c>
@@ -3128,7 +3142,7 @@
       </c>
       <c r="K80" s="8"/>
     </row>
-    <row r="81" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A81" s="7">
         <v>76</v>
       </c>
@@ -3151,7 +3165,7 @@
       </c>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A82" s="7">
         <v>77</v>
       </c>
@@ -3174,7 +3188,7 @@
       </c>
       <c r="K82" s="8"/>
     </row>
-    <row r="83" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A83" s="15">
         <v>78</v>
       </c>
@@ -3197,7 +3211,7 @@
       </c>
       <c r="K83" s="16"/>
     </row>
-    <row r="84" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A84" s="7">
         <v>79</v>
       </c>
@@ -3220,7 +3234,7 @@
       </c>
       <c r="K84" s="8"/>
     </row>
-    <row r="85" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A85" s="7">
         <v>80</v>
       </c>
@@ -3243,7 +3257,7 @@
       </c>
       <c r="K85" s="8"/>
     </row>
-    <row r="86" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A86" s="7">
         <v>81</v>
       </c>
@@ -3266,7 +3280,7 @@
       </c>
       <c r="K86" s="8"/>
     </row>
-    <row r="87" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A87" s="12">
         <v>82</v>
       </c>
@@ -3291,7 +3305,7 @@
       </c>
       <c r="K87" s="13"/>
     </row>
-    <row r="88" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A88" s="15">
         <v>83</v>
       </c>
@@ -3314,7 +3328,7 @@
       </c>
       <c r="K88" s="16"/>
     </row>
-    <row r="89" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A89" s="7">
         <v>84</v>
       </c>
@@ -3337,7 +3351,7 @@
       </c>
       <c r="K89" s="8"/>
     </row>
-    <row r="90" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A90" s="15">
         <v>85</v>
       </c>
@@ -3360,7 +3374,7 @@
       </c>
       <c r="K90" s="16"/>
     </row>
-    <row r="91" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A91" s="7">
         <v>86</v>
       </c>
@@ -3383,7 +3397,7 @@
       </c>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A92" s="15">
         <v>87</v>
       </c>
@@ -3406,7 +3420,7 @@
       </c>
       <c r="K92" s="16"/>
     </row>
-    <row r="93" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A93" s="7">
         <v>88</v>
       </c>
@@ -3429,7 +3443,7 @@
       </c>
       <c r="K93" s="8"/>
     </row>
-    <row r="94" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:11" ht="15.95" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A94" s="7">
         <v>89</v>
       </c>
@@ -3452,7 +3466,7 @@
       </c>
       <c r="K94" s="8"/>
     </row>
-    <row r="95" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:11" ht="14.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.15">
       <c r="A95" s="4">
         <v>90</v>
       </c>
@@ -3479,7 +3493,7 @@
       </c>
       <c r="K95" s="5"/>
     </row>
-    <row r="96" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A96" s="12">
         <v>91</v>
       </c>
@@ -3504,7 +3518,7 @@
       </c>
       <c r="K96" s="13"/>
     </row>
-    <row r="97" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A97" s="15">
         <v>92</v>
       </c>
@@ -3527,7 +3541,7 @@
       </c>
       <c r="K97" s="16"/>
     </row>
-    <row r="98" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A98" s="7">
         <v>93</v>
       </c>
@@ -3550,7 +3564,7 @@
       </c>
       <c r="K98" s="8"/>
     </row>
-    <row r="99" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A99" s="15">
         <v>94</v>
       </c>
@@ -3573,7 +3587,7 @@
       </c>
       <c r="K99" s="16"/>
     </row>
-    <row r="100" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A100" s="7">
         <v>95</v>
       </c>
@@ -3596,7 +3610,7 @@
       </c>
       <c r="K100" s="8"/>
     </row>
-    <row r="101" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A101" s="7">
         <v>96</v>
       </c>
@@ -3619,7 +3633,7 @@
       </c>
       <c r="K101" s="8"/>
     </row>
-    <row r="102" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A102" s="15">
         <v>97</v>
       </c>
@@ -3642,7 +3656,7 @@
       </c>
       <c r="K102" s="16"/>
     </row>
-    <row r="103" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A103" s="7">
         <v>98</v>
       </c>
@@ -3665,7 +3679,7 @@
       </c>
       <c r="K103" s="8"/>
     </row>
-    <row r="104" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A104" s="7">
         <v>99</v>
       </c>
@@ -3690,7 +3704,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A105" s="12">
         <v>100</v>
       </c>
@@ -3715,7 +3729,7 @@
       </c>
       <c r="K105" s="13"/>
     </row>
-    <row r="106" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A106" s="15">
         <v>101</v>
       </c>
@@ -3738,7 +3752,7 @@
       </c>
       <c r="K106" s="16"/>
     </row>
-    <row r="107" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A107" s="7">
         <v>102</v>
       </c>
@@ -3761,7 +3775,7 @@
       </c>
       <c r="K107" s="8"/>
     </row>
-    <row r="108" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A108" s="15">
         <v>103</v>
       </c>
@@ -3784,7 +3798,7 @@
       </c>
       <c r="K108" s="16"/>
     </row>
-    <row r="109" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A109" s="7">
         <v>104</v>
       </c>
@@ -3807,7 +3821,7 @@
       </c>
       <c r="K109" s="8"/>
     </row>
-    <row r="110" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A110" s="7">
         <v>105</v>
       </c>
@@ -3830,7 +3844,7 @@
       </c>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A111" s="15">
         <v>106</v>
       </c>
@@ -3853,7 +3867,7 @@
       </c>
       <c r="K111" s="16"/>
     </row>
-    <row r="112" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A112" s="7">
         <v>107</v>
       </c>
@@ -3876,7 +3890,7 @@
       </c>
       <c r="K112" s="8"/>
     </row>
-    <row r="113" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:11" ht="15.95" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A113" s="7">
         <v>108</v>
       </c>
@@ -3899,7 +3913,7 @@
       </c>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:11" ht="14.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.15">
       <c r="A114" s="4">
         <v>109</v>
       </c>
@@ -3926,7 +3940,7 @@
       </c>
       <c r="K114" s="5"/>
     </row>
-    <row r="115" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A115" s="12">
         <v>110</v>
       </c>
@@ -3951,7 +3965,7 @@
       </c>
       <c r="K115" s="13"/>
     </row>
-    <row r="116" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A116" s="15">
         <v>111</v>
       </c>
@@ -3974,7 +3988,7 @@
       </c>
       <c r="K116" s="16"/>
     </row>
-    <row r="117" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A117" s="7">
         <v>112</v>
       </c>
@@ -3997,7 +4011,7 @@
       </c>
       <c r="K117" s="8"/>
     </row>
-    <row r="118" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A118" s="15">
         <v>113</v>
       </c>
@@ -4020,7 +4034,7 @@
       </c>
       <c r="K118" s="16"/>
     </row>
-    <row r="119" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A119" s="7">
         <v>114</v>
       </c>
@@ -4043,7 +4057,7 @@
       </c>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A120" s="15">
         <v>115</v>
       </c>
@@ -4066,7 +4080,7 @@
       </c>
       <c r="K120" s="16"/>
     </row>
-    <row r="121" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A121" s="7">
         <v>116</v>
       </c>
@@ -4089,7 +4103,7 @@
       </c>
       <c r="K121" s="8"/>
     </row>
-    <row r="122" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:11" ht="15.95" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A122" s="7">
         <v>117</v>
       </c>
@@ -4114,7 +4128,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:11" ht="14.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.15">
       <c r="A123" s="4">
         <v>118</v>
       </c>
@@ -4141,7 +4155,7 @@
       </c>
       <c r="K123" s="5"/>
     </row>
-    <row r="124" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A124" s="12">
         <v>119</v>
       </c>
@@ -4166,7 +4180,7 @@
       </c>
       <c r="K124" s="13"/>
     </row>
-    <row r="125" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A125" s="15">
         <v>120</v>
       </c>
@@ -4189,7 +4203,7 @@
       </c>
       <c r="K125" s="16"/>
     </row>
-    <row r="126" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A126" s="7">
         <v>121</v>
       </c>
@@ -4212,7 +4226,7 @@
       </c>
       <c r="K126" s="8"/>
     </row>
-    <row r="127" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A127" s="15">
         <v>122</v>
       </c>
@@ -4235,7 +4249,7 @@
       </c>
       <c r="K127" s="16"/>
     </row>
-    <row r="128" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A128" s="7">
         <v>123</v>
       </c>
@@ -4258,7 +4272,7 @@
       </c>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A129" s="7">
         <v>124</v>
       </c>
@@ -4281,7 +4295,7 @@
       </c>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A130" s="15">
         <v>125</v>
       </c>
@@ -4304,7 +4318,7 @@
       </c>
       <c r="K130" s="16"/>
     </row>
-    <row r="131" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A131" s="7">
         <v>126</v>
       </c>
@@ -4327,7 +4341,7 @@
       </c>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:11" ht="15.95" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A132" s="7">
         <v>127</v>
       </c>
@@ -4352,7 +4366,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:11" ht="14.1" customHeight="1" collapsed="1" x14ac:dyDescent="0.15">
       <c r="A133" s="4">
         <v>128</v>
       </c>
@@ -4379,7 +4393,7 @@
       </c>
       <c r="K133" s="5"/>
     </row>
-    <row r="134" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A134" s="12">
         <v>129</v>
       </c>
@@ -4404,7 +4418,7 @@
       </c>
       <c r="K134" s="13"/>
     </row>
-    <row r="135" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A135" s="15">
         <v>130</v>
       </c>
@@ -4427,7 +4441,7 @@
       </c>
       <c r="K135" s="16"/>
     </row>
-    <row r="136" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A136" s="7">
         <v>131</v>
       </c>
@@ -4450,7 +4464,7 @@
       </c>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A137" s="15">
         <v>132</v>
       </c>
@@ -4473,7 +4487,7 @@
       </c>
       <c r="K137" s="16"/>
     </row>
-    <row r="138" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A138" s="7">
         <v>133</v>
       </c>
@@ -4496,7 +4510,7 @@
       </c>
       <c r="K138" s="8"/>
     </row>
-    <row r="139" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A139" s="7">
         <v>134</v>
       </c>
@@ -4519,7 +4533,7 @@
       </c>
       <c r="K139" s="8"/>
     </row>
-    <row r="140" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A140" s="15">
         <v>135</v>
       </c>
@@ -4542,7 +4556,7 @@
       </c>
       <c r="K140" s="16"/>
     </row>
-    <row r="141" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A141" s="7">
         <v>136</v>
       </c>
@@ -4567,7 +4581,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:11" ht="14.1" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A142" s="7">
         <v>137</v>
       </c>
@@ -4590,7 +4604,7 @@
       </c>
       <c r="K142" s="8"/>
     </row>
-    <row r="143" spans="1:11" ht="15" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:11" ht="15" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A143" s="7">
         <v>138</v>
       </c>
@@ -4613,6 +4627,7 @@
       </c>
       <c r="K143" s="8"/>
     </row>
+    <row r="144" spans="1:11" collapsed="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A2:K142" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">

--- a/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
+++ b/DOC/基本設計書/ソフトウェア仕様書_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abbbb\Documents\RiskMap\DOC\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A4A1DD-553C-41A5-874B-9E5F107CB653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B035B6-5496-4C47-AAF8-13458A6E1B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WBS!$A$2:$K$142</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -719,14 +719,14 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>着手中</t>
-    <rPh sb="0" eb="3">
-      <t>チャクシュチュウ</t>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>完了</t>
+    <t>着手中</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
     </rPh>
@@ -1262,17 +1262,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K144"/>
-  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:XFD144"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.375" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="16.625" customWidth="1"/>
     <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="9.875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="36.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="36.75" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="9" max="9" width="6.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
@@ -1997,7 +1997,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K31" s="5"/>
     </row>
@@ -2022,11 +2022,11 @@
         <v>16</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="K32" s="13"/>
     </row>
-    <row r="33" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A33" s="15">
         <v>28</v>
       </c>
@@ -2045,11 +2045,15 @@
         <v>16</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K33" s="16"/>
-    </row>
-    <row r="34" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD33">
+        <f>SUM(A33:XFC33)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A34" s="7">
         <v>29</v>
       </c>
@@ -2068,11 +2072,15 @@
         <v>16</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K34" s="8"/>
-    </row>
-    <row r="35" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD34">
+        <f>SUM(A34:XFC34)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A35" s="7">
         <v>30</v>
       </c>
@@ -2091,11 +2099,15 @@
         <v>16</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="K35" s="8"/>
-    </row>
-    <row r="36" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD35">
+        <f>SUM(A35:XFC35)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A36" s="15">
         <v>31</v>
       </c>
@@ -2113,12 +2125,16 @@
       <c r="I36" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J36" s="15" t="s">
-        <v>17</v>
+      <c r="J36" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="K36" s="16"/>
-    </row>
-    <row r="37" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD36">
+        <f>SUM(A36:XFC36)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A37" s="7">
         <v>32</v>
       </c>
@@ -2137,11 +2153,15 @@
         <v>16</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K37" s="8"/>
-    </row>
-    <row r="38" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD37">
+        <f>SUM(A37:XFC37)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A38" s="7">
         <v>33</v>
       </c>
@@ -2160,11 +2180,15 @@
         <v>16</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K38" s="8"/>
-    </row>
-    <row r="39" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD38">
+        <f>SUM(A38:XFC38)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A39" s="7">
         <v>34</v>
       </c>
@@ -2183,11 +2207,15 @@
         <v>16</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K39" s="8"/>
-    </row>
-    <row r="40" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD39">
+        <f>SUM(A39:XFC39)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A40" s="15">
         <v>35</v>
       </c>
@@ -2205,12 +2233,16 @@
       <c r="I40" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J40" s="15" t="s">
-        <v>17</v>
+      <c r="J40" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="K40" s="16"/>
-    </row>
-    <row r="41" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD40">
+        <f>SUM(A40:XFC40)</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A41" s="7">
         <v>36</v>
       </c>
@@ -2229,11 +2261,15 @@
         <v>16</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K41" s="8"/>
-    </row>
-    <row r="42" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD41">
+        <f>SUM(A41:XFC41)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A42" s="7">
         <v>37</v>
       </c>
@@ -2252,11 +2288,15 @@
         <v>16</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K42" s="8"/>
-    </row>
-    <row r="43" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD42">
+        <f>SUM(A42:XFC42)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11 16384:16384" ht="14.1" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A43" s="7">
         <v>38</v>
       </c>
@@ -2275,11 +2315,15 @@
         <v>16</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>17</v>
+        <v>209</v>
       </c>
       <c r="K43" s="8"/>
-    </row>
-    <row r="44" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+      <c r="XFD43">
+        <f>SUM(A43:XFC43)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11 16384:16384" ht="14.1" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.15">
       <c r="A44" s="12">
         <v>39</v>
       </c>
@@ -2304,7 +2348,7 @@
       </c>
       <c r="K44" s="13"/>
     </row>
-    <row r="45" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:11 16384:16384" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A45" s="15">
         <v>40</v>
       </c>
@@ -2327,7 +2371,7 @@
       </c>
       <c r="K45" s="16"/>
     </row>
-    <row r="46" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:11 16384:16384" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
         <v>41</v>
       </c>
@@ -2350,7 +2394,7 @@
       </c>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:11 16384:16384" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A47" s="7">
         <v>42</v>
       </c>
@@ -2373,7 +2417,7 @@
       </c>
       <c r="K47" s="8"/>
     </row>
-    <row r="48" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:11 16384:16384" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A48" s="15">
         <v>43</v>
       </c>
@@ -2396,7 +2440,7 @@
       </c>
       <c r="K48" s="16"/>
     </row>
-    <row r="49" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A49" s="7">
         <v>44</v>
       </c>
@@ -2419,7 +2463,7 @@
       </c>
       <c r="K49" s="8"/>
     </row>
-    <row r="50" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A50" s="7">
         <v>45</v>
       </c>
@@ -2442,7 +2486,7 @@
       </c>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A51" s="7">
         <v>46</v>
       </c>
@@ -2465,7 +2509,7 @@
       </c>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A52" s="15">
         <v>47</v>
       </c>
@@ -2488,7 +2532,7 @@
       </c>
       <c r="K52" s="16"/>
     </row>
-    <row r="53" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A53" s="7">
         <v>48</v>
       </c>
@@ -2511,7 +2555,7 @@
       </c>
       <c r="K53" s="8"/>
     </row>
-    <row r="54" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A54" s="7">
         <v>49</v>
       </c>
@@ -2534,7 +2578,7 @@
       </c>
       <c r="K54" s="8"/>
     </row>
-    <row r="55" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A55" s="7">
         <v>50</v>
       </c>
@@ -2582,7 +2626,7 @@
       </c>
       <c r="K56" s="13"/>
     </row>
-    <row r="57" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A57" s="15">
         <v>52</v>
       </c>
@@ -2605,7 +2649,7 @@
       </c>
       <c r="K57" s="16"/>
     </row>
-    <row r="58" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A58" s="7">
         <v>53</v>
       </c>
@@ -2628,7 +2672,7 @@
       </c>
       <c r="K58" s="8"/>
     </row>
-    <row r="59" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A59" s="15">
         <v>54</v>
       </c>
@@ -2651,7 +2695,7 @@
       </c>
       <c r="K59" s="16"/>
     </row>
-    <row r="60" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
         <v>55</v>
       </c>
@@ -2674,7 +2718,7 @@
       </c>
       <c r="K60" s="8"/>
     </row>
-    <row r="61" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A61" s="7">
         <v>56</v>
       </c>
@@ -2697,7 +2741,7 @@
       </c>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A62" s="15">
         <v>57</v>
       </c>
@@ -2720,7 +2764,7 @@
       </c>
       <c r="K62" s="16"/>
     </row>
-    <row r="63" spans="1:11" ht="14.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:11" ht="14.1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A63" s="7">
         <v>58</v>
       </c>
@@ -2743,7 +2787,7 @@
       </c>
       <c r="K63" s="8"/>
     </row>
-    <row r="64" spans="1:11" ht="15.95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:11" ht="15.95" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.15">
       <c r="A64" s="7">
         <v>59</v>
       </c>
